--- a/Layout Polizas/RENOVACION/TECMA (OLMES)/FW56222I - IMS OP BASE CLIENTE _ TECMA.xlsx
+++ b/Layout Polizas/RENOVACION/TECMA (OLMES)/FW56222I - IMS OP BASE CLIENTE _ TECMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://axa365-my.sharepoint.com/personal/emanuelesau_mejia_consultor_axa_com_mx/Documents/01.WinDevice/Desktop/Area de Trabajo/PoC-Emision-Proceso/PoC-Proceso-Emision/Layout Polizas/RENOVACION/TECMA (OLMES)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_AD4D2F04E46CFB4ACB3E2039BD55EC1C683EDF24" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BFEC13B-D81E-461E-9AAD-EA9A6B9F1111}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_AD4D2F04E46CFB4ACB3E2039BD55EC1C683EDF24" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A934A5DC-9417-47F1-8BFC-ECFB267697D3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4497,7 +4497,9 @@
   <dimension ref="A1:K951"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
